--- a/output/roomself_excel/3883.xlsx
+++ b/output/roomself_excel/3883.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>202840</v>
+        <v>171117</v>
       </c>
       <c r="D2" t="n">
-        <v>3808</v>
+        <v>3404</v>
       </c>
       <c r="E2" t="n">
-        <v>621</v>
+        <v>579</v>
       </c>
       <c r="F2" t="n">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>113668</v>
+        <v>360646</v>
       </c>
       <c r="D3" t="n">
-        <v>2744</v>
+        <v>5748</v>
       </c>
       <c r="E3" t="n">
-        <v>315</v>
+        <v>928</v>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>53856</v>
+        <v>202840</v>
       </c>
       <c r="D4" t="n">
-        <v>1900</v>
+        <v>3808</v>
       </c>
       <c r="E4" t="n">
-        <v>576</v>
+        <v>621</v>
       </c>
       <c r="F4" t="n">
-        <v>187</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>132816</v>
+        <v>113668</v>
       </c>
       <c r="D5" t="n">
-        <v>3112</v>
+        <v>2744</v>
       </c>
       <c r="E5" t="n">
-        <v>428</v>
+        <v>315</v>
       </c>
       <c r="F5" t="n">
-        <v>356</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>231064</v>
+        <v>132816</v>
       </c>
       <c r="D6" t="n">
-        <v>6168</v>
+        <v>3112</v>
       </c>
       <c r="E6" t="n">
-        <v>930</v>
+        <v>428</v>
       </c>
       <c r="F6" t="n">
-        <v>852</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56520</v>
+        <v>53856</v>
       </c>
       <c r="D8" t="n">
-        <v>1976</v>
+        <v>1900</v>
       </c>
       <c r="E8" t="n">
-        <v>341</v>
+        <v>187</v>
       </c>
       <c r="F8" t="n">
-        <v>207</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>663995</v>
+        <v>22446</v>
       </c>
       <c r="D9" t="n">
-        <v>12740</v>
+        <v>1292</v>
       </c>
       <c r="E9" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>123504</v>
+        <v>38934</v>
       </c>
       <c r="D10" t="n">
-        <v>2816</v>
+        <v>1580</v>
       </c>
       <c r="E10" t="n">
-        <v>390</v>
+        <v>206</v>
       </c>
       <c r="F10" t="n">
-        <v>360</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>350109</v>
+        <v>231064</v>
       </c>
       <c r="D11" t="n">
-        <v>6816</v>
+        <v>6168</v>
       </c>
       <c r="E11" t="n">
-        <v>196</v>
+        <v>498</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>63712</v>
+        <v>132232</v>
       </c>
       <c r="D12" t="n">
-        <v>2152</v>
+        <v>4572</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22446</v>
+        <v>33320</v>
       </c>
       <c r="D13" t="n">
-        <v>1292</v>
+        <v>1524</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>76000</v>
+        <v>56520</v>
       </c>
       <c r="D14" t="n">
-        <v>2320</v>
+        <v>1976</v>
       </c>
       <c r="E14" t="n">
-        <v>229</v>
+        <v>341</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -752,14 +752,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>207064</v>
+        <v>63712</v>
       </c>
       <c r="D15" t="n">
-        <v>3736</v>
+        <v>2152</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38934</v>
+        <v>276389</v>
       </c>
       <c r="D16" t="n">
-        <v>1580</v>
+        <v>4508</v>
       </c>
       <c r="E16" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30618</v>
+        <v>207064</v>
       </c>
       <c r="D17" t="n">
-        <v>1404</v>
+        <v>3736</v>
       </c>
       <c r="E17" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,86 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>33320</v>
+        <v>123504</v>
       </c>
       <c r="D18" t="n">
-        <v>1524</v>
+        <v>2816</v>
       </c>
       <c r="E18" t="n">
-        <v>301</v>
+        <v>344</v>
       </c>
       <c r="F18" t="n">
-        <v>88</v>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>73720</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2312</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>76000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2320</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>30618</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1404</v>
+      </c>
+      <c r="E21" t="n">
+        <v>162</v>
+      </c>
+      <c r="F21" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/3883.xlsx
+++ b/output/roomself_excel/3883.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>3404</v>
       </c>
-      <c r="E2" t="n">
-        <v>579</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>391</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>349</v>
+      </c>
+      <c r="J2" t="n">
+        <v>28</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>5748</v>
       </c>
-      <c r="E3" t="n">
-        <v>928</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>480</v>
-      </c>
+        <v>844</v>
+      </c>
+      <c r="G3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>538</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +592,38 @@
       <c r="D4" t="n">
         <v>3808</v>
       </c>
-      <c r="E4" t="n">
-        <v>621</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>385</v>
+        <v>358</v>
+      </c>
+      <c r="G4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>568</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>26</v>
+      </c>
+      <c r="M4" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +641,23 @@
       <c r="D5" t="n">
         <v>2744</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>315</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>27</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +674,31 @@
       <c r="D6" t="n">
         <v>3112</v>
       </c>
-      <c r="E6" t="n">
-        <v>428</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>343</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>401</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +715,38 @@
       <c r="D7" t="n">
         <v>3000</v>
       </c>
-      <c r="E7" t="n">
-        <v>416</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>373</v>
+      </c>
+      <c r="G7" t="n">
+        <v>27</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>377</v>
+      </c>
+      <c r="M7" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +764,23 @@
       <c r="D8" t="n">
         <v>1900</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>187</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>27</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +797,15 @@
       <c r="D9" t="n">
         <v>1292</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +822,23 @@
       <c r="D10" t="n">
         <v>1580</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>206</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>28</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +855,31 @@
       <c r="D11" t="n">
         <v>6168</v>
       </c>
-      <c r="E11" t="n">
-        <v>498</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>116</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>124</v>
+      </c>
+      <c r="J11" t="n">
+        <v>27</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +896,23 @@
       <c r="D12" t="n">
         <v>4572</v>
       </c>
-      <c r="E12" t="n">
-        <v>185</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>116</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="G12" t="n">
+        <v>28</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +929,31 @@
       <c r="D13" t="n">
         <v>1524</v>
       </c>
-      <c r="E13" t="n">
-        <v>301</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>88</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G13" t="n">
+        <v>28</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>245</v>
+      </c>
+      <c r="J13" t="n">
+        <v>28</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +970,31 @@
       <c r="D14" t="n">
         <v>1976</v>
       </c>
-      <c r="E14" t="n">
-        <v>341</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>207</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="G14" t="n">
+        <v>27</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>314</v>
+      </c>
+      <c r="J14" t="n">
+        <v>27</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1011,23 @@
       <c r="D15" t="n">
         <v>2152</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="G15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1044,15 @@
       <c r="D16" t="n">
         <v>4508</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1069,31 @@
       <c r="D17" t="n">
         <v>3736</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>362</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1110,31 @@
       <c r="D18" t="n">
         <v>2816</v>
       </c>
-      <c r="E18" t="n">
-        <v>344</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>248</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G18" t="n">
+        <v>28</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>220</v>
+      </c>
+      <c r="J18" t="n">
+        <v>28</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1151,15 @@
       <c r="D19" t="n">
         <v>2312</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1176,15 @@
       <c r="D20" t="n">
         <v>2320</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1201,23 @@
       <c r="D21" t="n">
         <v>1404</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>162</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>28</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/3883.xlsx
+++ b/output/roomself_excel/3883.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,66 @@
           <t>ExtWallWidth_3</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -535,6 +595,42 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>28</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>119</v>
+      </c>
+      <c r="U2" t="n">
+        <v>28</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -576,6 +672,54 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>540</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>28</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>237</v>
+      </c>
+      <c r="U3" t="n">
+        <v>28</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>82</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -624,6 +768,54 @@
       </c>
       <c r="M4" t="n">
         <v>26</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>27</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>168</v>
+      </c>
+      <c r="U4" t="n">
+        <v>27</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -658,6 +850,30 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>27</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -699,6 +915,42 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>27</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>59</v>
+      </c>
+      <c r="U6" t="n">
+        <v>27</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -748,6 +1000,30 @@
       <c r="M7" t="n">
         <v>27</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>27</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -781,6 +1057,30 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>27</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -806,6 +1106,18 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -839,6 +1151,30 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>28</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -880,6 +1216,30 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>307</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>27</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -913,6 +1273,30 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>28</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -954,6 +1338,42 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>28</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>98</v>
+      </c>
+      <c r="U13" t="n">
+        <v>28</v>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -995,6 +1415,42 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>27</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>117</v>
+      </c>
+      <c r="U14" t="n">
+        <v>27</v>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1028,6 +1484,30 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>18</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1053,6 +1533,18 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1094,6 +1586,30 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>241</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>20</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1135,6 +1651,30 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>28</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1160,6 +1700,18 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1185,6 +1737,18 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1218,6 +1782,30 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>28</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
